--- a/Trắc nghiệm ôn luyện/Embedded Hardware/multiple_choice_sample_template_EMBEDDED_PROTOCOLS.xlsx
+++ b/Trắc nghiệm ôn luyện/Embedded Hardware/multiple_choice_sample_template_EMBEDDED_PROTOCOLS.xlsx
@@ -453,19 +453,19 @@
         <v>UART là giao thức truyền thông bất đồng bộ nối tiếp, sử dụng dây Tx của thiết bị này nối với dây Rx của thiết bị kia và ngược lại, bắt buộc phải nối chung chân đất GND.</v>
       </c>
       <c r="E2" t="str">
+        <v>1 dây tín hiệu duy nhất không cần dây đất — giao thức 1-Wire</v>
+      </c>
+      <c r="F2" t="str">
         <v>2 dây: Tx (Truyền) và Rx (Nhận), dùng chung dây nối đất GND — 2 dây tín hiệu Tx Rx</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>3 dây: SDA, SCL và GND — giao thức I2C</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>4 dây: MISO, MOSI, SCK và SS — giao thức SPI</v>
       </c>
-      <c r="H2" t="str">
-        <v>1 dây tín hiệu duy nhất không cần dây đất — giao thức 1-Wire</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>Vì không có dây Clock dùng chung, hai thiết bị giao tiếp UART (bất đồng bộ) phải được cấu hình sẵn cùng một tốc độ truyền nhận (Baudrate) và cấu hình khung truyền (Start bit, Stop bit, Parity).</v>
       </c>
       <c r="E3" t="str">
+        <v>Bất đồng bộ chỉ truyền được dữ liệu dạng hình ảnh; còn đồng bộ chỉ truyền được dữ liệu số — loại dữ liệu truyền</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Bất đồng bộ có tốc độ truyền tải nhanh gấp 100 lần so với giao tiếp đồng bộ — tốc độ truyền tải</v>
+      </c>
+      <c r="G3" t="str">
         <v>Bất đồng bộ không sử dụng dây xung nhịp Clock (CLK) dùng chung; đồng bộ bắt buộc phải có dây Clock để đồng bộ hóa bit dữ liệu — không có dây Clock vs có dây Clock</v>
       </c>
-      <c r="F3" t="str">
-        <v>Bất đồng bộ chỉ truyền được dữ liệu dạng hình ảnh; còn đồng bộ chỉ truyền được dữ liệu số — loại dữ liệu truyền</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Bất đồng bộ bắt buộc phải chạy trên hệ điều hành RTOS; còn đồng bộ chạy Bare-metal — môi trường chạy phần mềm</v>
       </c>
-      <c r="H3" t="str">
-        <v>Bất đồng bộ có tốc độ truyền tải nhanh gấp 100 lần so với giao tiếp đồng bộ — tốc độ truyền tải</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>I2C là giao thức truyền thông nối tiếp đồng bộ, sử dụng 2 dây: SDA truyền nhận dữ liệu, SCL cấp xung nhịp clock đồng bộ.</v>
       </c>
       <c r="E4" t="str">
+        <v>CAN_H và CAN_L — giao thức CAN Bus</v>
+      </c>
+      <c r="F4" t="str">
+        <v>MOSI, MISO và SCK — giao thức SPI</v>
+      </c>
+      <c r="G4" t="str">
         <v>SDA (Dữ liệu nối tiếp) và SCL (Xung nhịp nối tiếp) — 2 dây Bus chung</v>
       </c>
-      <c r="F4" t="str">
+      <c r="H4" t="str">
         <v>Tx và Rx — giao thức UART</v>
       </c>
-      <c r="G4" t="str">
-        <v>MOSI, MISO và SCK — giao thức SPI</v>
-      </c>
-      <c r="H4" t="str">
-        <v>CAN_H và CAN_L — giao thức CAN Bus</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -540,19 +540,19 @@
         <v>Cấu trúc Open-drain của I2C cho phép nhiều thiết bị nối chung đường bus mà không lo chập mạch khi thiết bị này kéo bus xuống đất (Low) và thiết bị kia đẩy lên cao (High). Khi không có thiết bị nào kéo bus xuống đất, điện trở pull-up sẽ duy trì điện áp bus ở mức cao (High).</v>
       </c>
       <c r="E5" t="str">
+        <v>Để giảm thiểu dòng điện tiêu thụ của vi điều khiển xuống bằng 0 — tiết kiệm điện năng</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Để lọc các nhiễu sóng cao tần phát ra từ các thiết bị thu phát Wi-Fi bên ngoài — lọc nhiễu sóng</v>
+      </c>
+      <c r="G5" t="str">
         <v>Vì các chân I2C cấu hình ở dạng cực máng hở (Open-drain), điện trở kéo lên giúp kéo điện áp đường bus lên mức cao (Logical 1) khi bus rảnh — điện trở kéo lên cho cực máng hở Open-drain</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Để giảm thiểu dòng điện tiêu thụ của vi điều khiển xuống bằng 0 — tiết kiệm điện năng</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Để lọc các nhiễu sóng cao tần phát ra từ các thiết bị thu phát Wi-Fi bên ngoài — lọc nhiễu sóng</v>
       </c>
       <c r="H5" t="str">
         <v>Vì nếu không có điện trở, vi điều khiển sẽ bị cháy chip do hiện tượng đoản mạch phần cứng — bảo vệ đoản mạch</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -575,10 +575,10 @@
         <v>2 dây: SDA và SCL — giao thức I2C</v>
       </c>
       <c r="G6" t="str">
+        <v>2 dây: CAN_H và CAN_L — giao thức CAN Bus</v>
+      </c>
+      <c r="H6" t="str">
         <v>2 dây: Tx và Rx — giao thức UART</v>
-      </c>
-      <c r="H6" t="str">
-        <v>2 dây: CAN_H và CAN_L — giao thức CAN Bus</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -598,19 +598,19 @@
         <v>Khi Master muốn giao tiếp với Slave nào (trong mô hình nhiều Slave dùng chung bus SPI), Master sẽ kéo chân CS của Slave đó xuống mức thấp (Active Low) để đánh thức nó.</v>
       </c>
       <c r="E7" t="str">
-        <v>Được Master kéo xuống mức thấp (Low) để kích hoạt và lựa chọn chip Slave cụ thể muốn giao tiếp — chọn chip Slave tương tác</v>
+        <v>Tự động reset lại chip Slave khi phát sinh lỗi truyền dẫn dữ liệu — reset chip Slave</v>
       </c>
       <c r="F7" t="str">
         <v>Cấp nguồn điện 3.3V trực tiếp cho các linh kiện ngoại vi hoạt động — cấp nguồn điện vật lý</v>
       </c>
       <c r="G7" t="str">
+        <v>Được Master kéo xuống mức thấp (Low) để kích hoạt và lựa chọn chip Slave cụ thể muốn giao tiếp — chọn chip Slave tương tác</v>
+      </c>
+      <c r="H7" t="str">
         <v>Truyền nhận các mã lệnh điều khiển tốc độ xung nhịp của vi điều khiển — điều khiển xung nhịp clock</v>
       </c>
-      <c r="H7" t="str">
-        <v>Tự động reset lại chip Slave khi phát sinh lỗi truyền dẫn dữ liệu — reset chip Slave</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>Baudrate (ví dụ: 9600 bps, 115200 bps) là đơn vị đo tốc độ truyền thông nối tiếp, thể hiện số lượng đơn vị tín hiệu (bit) truyền đi trên đường dây trong 1 giây.</v>
       </c>
       <c r="E8" t="str">
+        <v>Số byte dữ liệu tối đa bộ đệm UART có thể chứa — dung lượng bộ đệm</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Thời gian trễ tính bằng mili-giây từ khi gửi đến khi nhận dữ liệu — độ trễ truyền dữ liệu</v>
+      </c>
+      <c r="G8" t="str">
         <v>Số lượng bit dữ liệu được truyền đi thành công trong một giây (bits per second) — tốc độ bit truyền nhận</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Số byte dữ liệu tối đa bộ đệm UART có thể chứa — dung lượng bộ đệm</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Thời gian trễ tính bằng mili-giây từ khi gửi đến khi nhận dữ liệu — độ trễ truyền dữ liệu</v>
       </c>
       <c r="H8" t="str">
         <v>Tần số dao động của bộ thạch anh nội vi của vi điều khiển — tần số thạch anh chip</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -656,19 +656,19 @@
         <v>I2C là giao thức định địa chỉ bằng phần mềm (Software Addressing). Mỗi Slave có một địa chỉ cố định. Khi bắt đầu khung truyền (Start condition), Master sẽ gửi địa chỉ Slave đó lên bus, các Slave khác đọc thấy không phải địa chỉ của mình sẽ bỏ qua.</v>
       </c>
       <c r="E9" t="str">
+        <v>Master bắt buộc phải gửi tin nhắn văn bản tiếng Việt yêu cầu Slave thức dậy — gửi tin nhắn văn bản</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Các Slave tự động chia ca hoạt động luân phiên theo thời gian thực — chia ca hoạt động</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Master kéo chân CS vật lý của Slave đó xuống đất — cơ chế CS của SPI</v>
+      </c>
+      <c r="H9" t="str">
         <v>Master gửi một khung truyền chứa địa chỉ vật lý duy nhất (Address - 7 bit hoặc 10 bit) của Slave đó lên bus — địa chỉ vật lý duy nhất của Slave</v>
       </c>
-      <c r="F9" t="str">
-        <v>Master kéo chân CS vật lý của Slave đó xuống đất — cơ chế CS của SPI</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Master bắt buộc phải gửi tin nhắn văn bản tiếng Việt yêu cầu Slave thức dậy — gửi tin nhắn văn bản</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Các Slave tự động chia ca hoạt động luân phiên theo thời gian thực — chia ca hoạt động</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>Khi có nhiễu điện từ bên ngoài tác động, nó sẽ tác động lên cả hai dây CAN_H và CAN_L cùng một lượng điện áp tương đương (nhiễu đồng pha - Common-mode noise). Phép trừ hiệu điện áp ở bộ thu sẽ tự động triệt tiêu lượng nhiễu này, giúp tín hiệu CAN cực kỳ ổn định.</v>
       </c>
       <c r="E10" t="str">
-        <v>Sử dụng truyền truyền tín hiệu vi sai (Differential Signaling) qua cặp dây xoắn CAN_H và CAN_L; bộ thu đọc hiệu điện áp chênh lệch ($V_{diff} = V_{CAN_H} - V_{CAN_L}$) giúp triệt tiêu nhiễu đồng pha — truyền tín hiệu vi sai triệt tiêu nhiễu đồng pha</v>
+        <v>Được bọc một lớp vỏ bằng lá chì dày 5cm xung quanh toàn bộ đường dây dẫn — bọc lá chì bảo vệ</v>
       </c>
       <c r="F10" t="str">
         <v>Sử dụng cáp quang bằng thủy tinh để truyền dữ liệu bằng ánh sáng thay vì dòng điện — truyền bằng cáp quang</v>
       </c>
       <c r="G10" t="str">
-        <v>Được bọc một lớp vỏ bằng lá chì dày 5cm xung quanh toàn bộ đường dây dẫn — bọc lá chì bảo vệ</v>
+        <v>Tự động tăng điện áp truyền dẫn lên mức 1000V để vượt qua các nguồn nhiễu — tăng điện áp cực đoan</v>
       </c>
       <c r="H10" t="str">
-        <v>Tự động tăng điện áp truyền dẫn lên mức 1000V để vượt qua các nguồn nhiễu — tăng điện áp cực đoan</v>
+        <v>Sử dụng truyền truyền tín hiệu vi sai (Differential Signaling) qua cặp dây xoắn CAN_H và CAN_L; bộ thu đọc hiệu điện áp chênh lệch ($V_{diff} = V_{CAN_H} - V_{CAN_L}$) giúp triệt tiêu nhiễu đồng pha — truyền tín hiệu vi sai triệt tiêu nhiễu đồng pha</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -717,13 +717,13 @@
         <v>CPOL định nghĩa trạng thái của đường clock khi rảnh (Idle state); CPHA định nghĩa sườn xung clock (sườn lên hay sườn xuống) dùng để chốt mẫu dữ liệu (sample data) — cực tính và pha của xung nhịp clock</v>
       </c>
       <c r="F11" t="str">
+        <v>CPOL bắt buộc phải bằng 1 và CPHA bắt buộc phải bằng 0 trong mọi trường hợp kết nối — giá trị cấu hình cố định</v>
+      </c>
+      <c r="G11" t="str">
         <v>CPOL định nghĩa độ dài của bit dữ liệu truyền; CPHA định nghĩa tốc độ Baudrate của xung nhịp — độ dài bit và tốc độ</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>CPOL dùng để chọn chip Master; CPHA dùng để chọn chip Slave trong hệ thống — phân vai trò thiết bị</v>
-      </c>
-      <c r="H11" t="str">
-        <v>CPOL bắt buộc phải bằng 1 và CPHA bắt buộc phải bằng 0 trong mọi trường hợp kết nối — giá trị cấu hình cố định</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -749,10 +749,10 @@
         <v>Nút nào phát hiện va chạm sẽ tự động tăng công suất phát sóng để đè bẹp các tín hiệu của nút đối thủ — tăng công suất phát sóng</v>
       </c>
       <c r="G12" t="str">
+        <v>Master sẽ gửi lệnh ngắt ngẫu nhiên để chọn ra một nút ngẫu nhiên được quyền truyền tiếp — Master điều phối ngẫu nhiên</v>
+      </c>
+      <c r="H12" t="str">
         <v>Tất cả các nút đang truyền sẽ dừng lại, hệ thống tự động reset lại nguồn của xe ô tô — reset nguồn xe</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Master sẽ gửi lệnh ngắt ngẫu nhiên để chọn ra một nút ngẫu nhiên được quyền truyền tiếp — Master điều phối ngẫu nhiên</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -772,19 +772,19 @@
         <v>Mức TTL (0-3.3V) có biên nhiễu rất nhỏ, chạy dây dài sẽ bị nhiễu làm sai bit dữ liệu. RS232 sử dụng điện áp âm/dương lớn (+/- 3V đến +/- 15V) giúp đi xa hơn (15m). RS485 sử dụng vi sai (A-B) giúp đi cực xa (lên tới 1200m) trong môi trường công nghiệp nhiễu nặng.</v>
       </c>
       <c r="E13" t="str">
-        <v>Vì mức tín hiệu TTL (0-3.3V/5V) dễ bị suy hao và nhiễu trên đường dây dài; giải pháp là sử dụng chip chuyển đổi sang chuẩn RS232 (mức điện áp cao +/-15V) hoặc RS485 (tín hiệu vi sai) — chuyển đổi sang chuẩn RS232 hoặc RS485 chống nhiễu khoảng cách xa</v>
+        <v>Vì dây dẫn dài sẽ làm tăng điện trở và làm cháy cổng UART của vi điều khiển — cháy cổng UART do điện trở</v>
       </c>
       <c r="F13" t="str">
-        <v>Vì dây dẫn dài sẽ làm tăng điện trở và làm cháy cổng UART của vi điều khiển — cháy cổng UART do điện trở</v>
+        <v>Yêu cầu vi điều khiển phải chạy bằng pin 12V thay vì nguồn USB 5V — thay đổi nguồn điện chip</v>
       </c>
       <c r="G13" t="str">
         <v>Giải pháp là tăng tốc độ Baudrate lên mức tối đa để dữ liệu đi nhanh hơn tránh bị nhiễu dọc đường — tăng baudrate sai phương pháp</v>
       </c>
       <c r="H13" t="str">
-        <v>Yêu cầu vi điều khiển phải chạy bằng pin 12V thay vì nguồn USB 5V — thay đổi nguồn điện chip</v>
+        <v>Vì mức tín hiệu TTL (0-3.3V/5V) dễ bị suy hao và nhiễu trên đường dây dài; giải pháp là sử dụng chip chuyển đổi sang chuẩn RS232 (mức điện áp cao +/-15V) hoặc RS485 (tín hiệu vi sai) — chuyển đổi sang chuẩn RS232 hoặc RS485 chống nhiễu khoảng cách xa</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         <v>Đây là quy định vật lý của I2C. Khi bus rảnh, cả SDA và SCL đều ở mức High (nhờ điện trở pull-up). Khi bắt đầu truyền, Master tạo ra START condition. Quy tắc: Dữ liệu trên dây SDA chỉ được phép thay đổi khi SCL đang ở mức Low, và phải giữ nguyên khi SCL ở mức High, ngoại trừ điều kiện START và STOP.</v>
       </c>
       <c r="E14" t="str">
+        <v>START: Master kéo chân CS của Slave xuống đất; STOP: Master kéo chân CS lên mức cao — cơ chế CS của SPI</v>
+      </c>
+      <c r="F14" t="str">
+        <v>START: Gửi ký tự byte `0x02` (STX); STOP: Gửi ký tự byte `0x03` (ETX) — ký tự điều khiển ASCII</v>
+      </c>
+      <c r="G14" t="str">
+        <v>START: Trực tiếp cấp nguồn điện cho đường bus; STOP: Tắt nguồn điện của vi điều khiển — cấp ngắt nguồn điện</v>
+      </c>
+      <c r="H14" t="str">
         <v>START: SDA chuyển từ High sang Low khi SCL đang ở mức High; STOP: SDA chuyển từ Low sang High khi SCL đang ở mức High — START/STOP conditions của bus I2C</v>
       </c>
-      <c r="F14" t="str">
-        <v>START: Trực tiếp cấp nguồn điện cho đường bus; STOP: Tắt nguồn điện của vi điều khiển — cấp ngắt nguồn điện</v>
-      </c>
-      <c r="G14" t="str">
-        <v>START: Master kéo chân CS của Slave xuống đất; STOP: Master kéo chân CS lên mức cao — cơ chế CS của SPI</v>
-      </c>
-      <c r="H14" t="str">
-        <v>START: Gửi ký tự byte `0x02` (STX); STOP: Gửi ký tự byte `0x03` (ETX) — ký tự điều khiển ASCII</v>
-      </c>
       <c r="I14">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>Xung điện truyền trên đường bus khi gặp điểm cuối dây (mở mạch) sẽ bị dội ngược lại (phản xạ), va chạm với các xung tiếp theo gây méo mó dạng sóng. Hai điện trở 120 Ohm mắc song song tạo ra trở kháng tương đương 60 Ohm khớp với trở kháng đặc tính của cáp CAN, hấp thụ hoàn toàn năng lượng sóng dội ngược.</v>
       </c>
       <c r="E15" t="str">
-        <v>Để triệt tiêu hiện tượng phản xạ tín hiệu (Signal Reflection) trên đường dây truyền dẫn dài, tránh làm biến dạng xung tín hiệu gây lỗi bit — triệt tiêu phản xạ tín hiệu</v>
+        <v>Để tăng tốc độ truyền dữ liệu của bus CAN lên mức tối đa 100 Mbps — tăng tốc độ bus CAN</v>
       </c>
       <c r="F15" t="str">
         <v>Để hạn chế dòng điện chạy qua dây dẫn tránh gây chập cháy hộp đen xe hơi — hạn chế dòng điện</v>
       </c>
       <c r="G15" t="str">
-        <v>Để tăng tốc độ truyền dữ liệu của bus CAN lên mức tối đa 100 Mbps — tăng tốc độ bus CAN</v>
+        <v>Để lọc các tần số nhiễu sinh ra từ bugi đánh lửa của động cơ xe ô tô — lọc nhiễu bugi</v>
       </c>
       <c r="H15" t="str">
-        <v>Để lọc các tần số nhiễu sinh ra từ bugi đánh lửa của động cơ xe ô tô — lọc nhiễu bugi</v>
+        <v>Để triệt tiêu hiện tượng phản xạ tín hiệu (Signal Reflection) trên đường dây truyền dẫn dài, tránh làm biến dạng xung tín hiệu gây lỗi bit — triệt tiêu phản xạ tín hiệu</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -862,10 +862,10 @@
         <v>Dùng để phát hiện lỗi bit đơn bằng cách đếm số lượng bit 1 là chẵn (Even) hay lẻ (Odd); giới hạn là không thể phát hiện lỗi nếu bị sai lệch đồng thời 2 bit — phát hiện lỗi bit đơn và giới hạn lỗi kép</v>
       </c>
       <c r="F16" t="str">
+        <v>Dùng để định vị địa chỉ của chip Slave nhận dữ liệu tiếp theo — định địa chỉ thiết bị</v>
+      </c>
+      <c r="G16" t="str">
         <v>Dùng để mã hóa bảo mật dữ liệu trước khi gửi lên đường truyền mạng — mã hóa dữ liệu</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Dùng để định vị địa chỉ của chip Slave nhận dữ liệu tiếp theo — định địa chỉ thiết bị</v>
       </c>
       <c r="H16" t="str">
         <v>Dùng để chỉ định sườn xung clock bắt đầu đọc dữ liệu mẫu — sườn xung clock</v>
@@ -888,19 +888,19 @@
         <v>I2C sử dụng cơ chế Wired-AND (nối cổng AND vật lý qua điện trở kéo lên). Master khi truyền luôn luôn lắng nghe trạng thái thực tế của đường bus SDA. Nếu nó gửi bit 1 (High) nhưng đọc thấy bus là 0 (Low - do Master kia kéo xuống), nó hiểu là đã thua cuộc trong quá trình Arbitration và lập tức rút lui nhường bus cho Master thắng cuộc.</v>
       </c>
       <c r="E17" t="str">
-        <v>Sử dụng cơ chế phân định bus (Bus Arbitration): Master nào đọc thấy đường SDA bị kéo xuống Low (bởi Master kia) trong khi nó muốn gửi High sẽ tự động dừng truyền và chuyển sang chế độ chờ — phân định bus dựa trên giám sát SDA</v>
+        <v>Hệ thống tự động kích hoạt ngắt reset nguồn của toàn bộ vi điều khiển trên mạch — reset nguồn</v>
       </c>
       <c r="F17" t="str">
         <v>Master nào có kích thước vật lý lớn hơn sẽ được ưu tiên chiếm quyền truyền trước — kích thước vật lý</v>
       </c>
       <c r="G17" t="str">
+        <v>Sử dụng cơ chế phân định bus (Bus Arbitration): Master nào đọc thấy đường SDA bị kéo xuống Low (bởi Master kia) trong khi nó muốn gửi High sẽ tự động dừng truyền và chuyển sang chế độ chờ — phân định bus dựa trên giám sát SDA</v>
+      </c>
+      <c r="H17" t="str">
         <v>Cả hai Master sẽ cùng truyền chèn đè tín hiệu lên nhau cho đến khi một trong hai bị hỏng chip — chèn đè tín hiệu</v>
       </c>
-      <c r="H17" t="str">
-        <v>Hệ thống tự động kích hoạt ngắt reset nguồn của toàn bộ vi điều khiển trên mạch — reset nguồn</v>
-      </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -920,13 +920,13 @@
         <v>Tiết kiệm tối đa số lượng chân GPIO của Master vì tất cả các Slave dùng chung duy nhất một chân CS/SS chung — tiết kiệm chân GPIO Master nối tầng</v>
       </c>
       <c r="F18" t="str">
-        <v>Tốc độ truyền dữ liệu nhanh gấp 10 lần so với cách nối độc lập hình sao — tốc độ truyền tải</v>
+        <v>Hoàn toàn loại bỏ nhu cầu sử dụng dây xung nhịp SCK dùng chung — không dùng dây clock</v>
       </c>
       <c r="G18" t="str">
         <v>Mỗi Slave có thể tự đặt địa chỉ phần mềm độc lập giống giao thức I2C — định địa chỉ phần mềm</v>
       </c>
       <c r="H18" t="str">
-        <v>Hoàn toàn loại bỏ nhu cầu sử dụng dây xung nhịp SCK dùng chung — không dùng dây clock</v>
+        <v>Tốc độ truyền dữ liệu nhanh gấp 10 lần so với cách nối độc lập hình sao — tốc độ truyền tải</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -946,19 +946,19 @@
         <v>SPI là giao thức truyền dữ liệu chung, không có khái niệm chu kỳ thời gian thực cho audio frames. I2S là giao thức chuyên biệt cho âm thanh số, có 3 dây: SCK (xung nhịp bit), SD (dữ liệu), và WS (Word Select - xác định kênh Left/Right). WS giúp đồng bộ hóa chính xác tần số lấy mẫu (Sampling rate), triệt tiêu lỗi Jitter (lệch pha thời gian) gây rè hoặc mất tiếng của audio.</v>
       </c>
       <c r="E19" t="str">
-        <v>I2S có đường truyền xung nhịp clock chuyên biệt cho kênh âm thanh trái/phải (WS/LRCK) giúp đồng bộ hóa dữ liệu âm thanh chính xác tuyệt đối ở tần số lấy mẫu cố định, tránh hiện tượng lệch pha jitter — I2S đồng bộ hóa kênh âm thanh chuyên biệt</v>
+        <v>I2S tự động nén dữ liệu âm thanh sang định dạng file mp3 trước khi truyền về chip — tự động nén mp3</v>
       </c>
       <c r="F19" t="str">
         <v>SPI không hỗ trợ tốc độ truyền dẫn dữ liệu vượt quá 1 MHz — giới hạn tốc độ SPI</v>
       </c>
       <c r="G19" t="str">
-        <v>I2S tự động nén dữ liệu âm thanh sang định dạng file mp3 trước khi truyền về chip — tự động nén mp3</v>
+        <v>I2S có đường truyền xung nhịp clock chuyên biệt cho kênh âm thanh trái/phải (WS/LRCK) giúp đồng bộ hóa dữ liệu âm thanh chính xác tuyệt đối ở tần số lấy mẫu cố định, tránh hiện tượng lệch pha jitter — I2S đồng bộ hóa kênh âm thanh chuyên biệt</v>
       </c>
       <c r="H19" t="str">
         <v>I2S sử dụng tín hiệu vi sai giúp chống nhiễu tốt hơn SPI gấp 100 lần trên đường dây dài — so sánh chống nhiễu vi sai</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -978,13 +978,13 @@
         <v>Bộ điều khiển CAN của mỗi nút tự động đếm lỗi (TEC và REC): Nếu lỗi liên tục vượt ngưỡng 255 (Transmit Error Counter &gt; 255), nút đó tự động ngắt kết nối vật lý khỏi bus (chuyển sang trạng thái Bus-off) để bảo vệ mạng — cơ chế tự động cô lập nút lỗi Bus-off</v>
       </c>
       <c r="F20" t="str">
+        <v>Tất cả các ECU khác sẽ tự động tăng điện áp truyền của mình lên mức 12V để đè bẹp Error Frames — tăng điện áp đè bẹp</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Đường dây bus CAN tự động kích hoạt một cầu chì nhiệt vật lý để ngắt kết nối nút bị chập — cầu chì nhiệt vật lý</v>
+      </c>
+      <c r="H20" t="str">
         <v>Master sẽ gửi lệnh ngắt nguồn điện cấp cho ECU bị lỗi đó thông qua mạng không dây Wi-Fi — tắt nguồn chéo chéo</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Tất cả các ECU khác sẽ tự động tăng điện áp truyền của mình lên mức 12V để đè bẹp Error Frames — tăng điện áp đè bẹp</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Đường dây bus CAN tự động kích hoạt một cầu chì nhiệt vật lý để ngắt kết nối nút bị chập — cầu chì nhiệt vật lý</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1004,19 +1004,19 @@
         <v>Modbus RTU truyền dữ liệu nhị phân thô, bất kỳ byte nào cũng có thể trùng với các mã điều khiển. Do đó, nó sử dụng định thời (Timing) để phân tách khung. Một khoảng lặng trên đường truyền kéo dài ít nhất 3.5 ký tự (ví dụ khoảng 4ms ở baudrate 9600) được coi là dấu hiệu kết thúc frame. Nếu khoảng nghỉ giữa các byte trong 1 frame vượt quá 1.5 ký tự, thiết bị nhận sẽ coi là frame bị lỗi và hủy bỏ.</v>
       </c>
       <c r="E21" t="str">
+        <v>Thời gian nghỉ tối thiểu bằng thời gian truyền 1 byte dữ liệu để giải phóng bộ nhớ đệm UART — giải phóng buffer</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Không cần thời gian nghỉ, các khung truyền có thể gửi liên tục gối đầu lên nhau để đạt hiệu năng tối đa — truyền liên tục</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Thời gian nghỉ cố định luôn luôn là 10 mili-giây đối với tất cả các tốc độ truyền — thời gian trễ cố định</v>
+      </c>
+      <c r="H21" t="str">
         <v>Thời gian nghỉ tối thiểu bằng thời gian truyền 3.5 ký tự (3.5 character time); để các thiết bị nhận biết được điểm kết thúc của khung cũ và điểm bắt đầu của khung mới do Modbus RTU không có start/stop bytes đặc biệt — Silent Interval 3.5 character time phân tách khung</v>
       </c>
-      <c r="F21" t="str">
-        <v>Thời gian nghỉ cố định luôn luôn là 10 mili-giây đối với tất cả các tốc độ truyền — thời gian trễ cố định</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Thời gian nghỉ tối thiểu bằng thời gian truyền 1 byte dữ liệu để giải phóng bộ nhớ đệm UART — giải phóng buffer</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Không cần thời gian nghỉ, các khung truyền có thể gửi liên tục gối đầu lên nhau để đạt hiệu năng tối đa — truyền liên tục</v>
-      </c>
       <c r="I21">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1036,13 +1036,13 @@
         <v>Nguy hiểm vì điện áp 5V từ pull-up của cảm biến có thể bơm dòng ngược làm hỏng chân GPIO của vi điều khiển 3.3V; giải pháp là sử dụng mạch chuyển đổi mức logic hai chiều (Bidirectional Logic Level Shifter) dùng Transistor MOSFET — mạch chuyển đổi mức logic hai chiều MOSFET</v>
       </c>
       <c r="F22" t="str">
-        <v>Nguy hiểm vì cảm biến sẽ bị thiếu nguồn điện hoạt động và tự động sập nguồn; giải pháp là nối thêm một chiếc pin 9V vào mạch — nối pin phụ</v>
+        <v>Nguy hiểm vì tốc độ xung nhịp SCL của cảm biến sẽ bị giảm đi một nửa; giải pháp là tăng tần số thạch anh ngoại vi — tăng tần số thạch anh</v>
       </c>
       <c r="G22" t="str">
         <v>Giải pháp là lập trình viết code tăng điện áp đầu ra của chân GPIO vi điều khiển lên mức 5V — lập trình tăng điện áp GPIO</v>
       </c>
       <c r="H22" t="str">
-        <v>Nguy hiểm vì tốc độ xung nhịp SCL của cảm biến sẽ bị giảm đi một nửa; giải pháp là tăng tần số thạch anh ngoại vi — tăng tần số thạch anh</v>
+        <v>Nguy hiểm vì cảm biến sẽ bị thiếu nguồn điện hoạt động và tự động sập nguồn; giải pháp là nối thêm một chiếc pin 9V vào mạch — nối pin phụ</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -1062,19 +1062,19 @@
         <v>TCP có cơ chế bắt tay 3 bước (3-way handshake) và gửi lại gói tin bị mất (Automatic Repeat Request), tạo ra độ trễ (latency) không đoán trước được. UDP không duy trì kết nối, bắn gói tin đi ngay lập tức. Trong thu thập dữ liệu cảm biến thời gian thực (như đo góc máy bay), dữ liệu mới quan trọng nhất. Nếu mất gói tin cũ, việc gửi lại (của TCP) chỉ làm nghẽn băng thông và làm sai lệch thời gian thực của dữ liệu mới, do đó chọn UDP/IP.</v>
       </c>
       <c r="E23" t="str">
-        <v>TCP hướng kết nối, đảm bảo truyền tin cậy, sửa lỗi bằng cách gửi lại (retry - chậm hơn); UDP không kết nối, truyền nhanh, không đảm bảo sửa lỗi; chọn UDP khi cần truyền tốc độ cao dữ liệu cảm biến định kỳ liên tục, chấp nhận mất mát vài gói tin cũ — TCP tin cậy chậm vs UDP nhanh không kết nối thích hợp streaming dữ liệu cảm biến</v>
+        <v>TCP bắt buộc phải mã hóa dữ liệu bằng thuật toán AES; còn UDP hoàn toàn không hỗ trợ bảo mật — phân loại bảo mật</v>
       </c>
       <c r="F23" t="str">
         <v>TCP chỉ chạy được trên mạng cáp đồng; còn UDP chỉ chạy được trên mạng không dây Wi-Fi — phân loại môi trường truyền</v>
       </c>
       <c r="G23" t="str">
-        <v>TCP bắt buộc phải mã hóa dữ liệu bằng thuật toán AES; còn UDP hoàn toàn không hỗ trợ bảo mật — phân loại bảo mật</v>
+        <v>TCP hướng kết nối, đảm bảo truyền tin cậy, sửa lỗi bằng cách gửi lại (retry - chậm hơn); UDP không kết nối, truyền nhanh, không đảm bảo sửa lỗi; chọn UDP khi cần truyền tốc độ cao dữ liệu cảm biến định kỳ liên tục, chấp nhận mất mát vài gói tin cũ — TCP tin cậy chậm vs UDP nhanh không kết nối thích hợp streaming dữ liệu cảm biến</v>
       </c>
       <c r="H23" t="str">
         <v>TCP luôn luôn tiêu thụ năng lượng của chip ít hơn gấp 10 lần so với giao thức UDP — so sánh tiêu thụ điện năng</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>USB HID rất phổ biến cho các thiết bị điều khiển vì tính tiện lợi (Plug and Play), hệ điều hành Windows/Linux/Mac tích hợp sẵn driver chuẩn của nó. USB CDC (Virtual COM Port) yêu cầu cài đặt driver CDC (trên Windows cũ) và thích hợp để tạo giao diện dòng lệnh (CLI) gỡ lỗi hoặc truyền nhận file thô giữa MCU và PC.</v>
       </c>
       <c r="E24" t="str">
-        <v>HID dùng cho các thiết bị tương tác người dùng (chuột, bàn phím) chạy không cần cài đặt driver trên máy tính; CDC giả lập cổng COM ảo nối tiếp dùng để truyền nhận dữ liệu tự do — HID cắm chạy không driver vs CDC giả lập COM truyền dữ liệu tự do</v>
+        <v>HID bắt buộc phải sử dụng cáp kết nối USB-C; còn CDC chỉ hỗ trợ cổng USB Type-A cũ — loại cổng cắm vật lý</v>
       </c>
       <c r="F24" t="str">
         <v>HID chỉ hỗ trợ truyền dữ liệu tốc độ 115200 bps; còn CDC hỗ trợ tốc độ không giới hạn — so sánh tốc độ</v>
       </c>
       <c r="G24" t="str">
-        <v>HID bắt buộc phải sử dụng cáp kết nối USB-C; còn CDC chỉ hỗ trợ cổng USB Type-A cũ — loại cổng cắm vật lý</v>
+        <v>HID dùng cho các thiết bị tương tác người dùng (chuột, bàn phím) chạy không cần cài đặt driver trên máy tính; CDC giả lập cổng COM ảo nối tiếp dùng để truyền nhận dữ liệu tự do — HID cắm chạy không driver vs CDC giả lập COM truyền dữ liệu tự do</v>
       </c>
       <c r="H24" t="str">
         <v>HID chỉ dành cho hệ điều hành Windows; còn CDC chỉ dành riêng cho Linux — hệ điều hành hỗ trợ</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Chế độ Parasite Power (nguồn ký sinh) của 1-Wire cho phép chip sạc một tụ điện nội vi khi đường truyền ở mức High, và dùng năng lượng đó để hoạt động khi đường truyền kéo xuống Low để gửi dữ liệu. Nhờ đó, cảm biến chỉ cần 2 dây (1 dây Data/Power + 1 dây Ground) để hoạt động, giảm tối đa số lõi dây dẫn.</v>
       </c>
       <c r="E25" t="str">
+        <v>Truyền tín hiệu thông qua sóng vô tuyến hồng ngoại không cần dây dẫn vật lý — hồng ngoại không dây</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Bắt buộc phải sử dụng các sợi dây cáp đồng có đường kính lõi lớn hơn 5mm — đường kính dây dẫn lõi lớn</v>
+      </c>
+      <c r="G25" t="str">
         <v>Chỉ sử dụng duy nhất một dây tín hiệu chung cho cả việc cấp nguồn điện (Parasite Power mode) và truyền dữ liệu hai chiều, dùng chung dây GND — 1 dây tín hiệu kiêm cấp nguồn parasite power</v>
       </c>
-      <c r="F25" t="str">
-        <v>Truyền tín hiệu thông qua sóng vô tuyến hồng ngoại không cần dây dẫn vật lý — hồng ngoại không dây</v>
-      </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>Tự động đồng bộ hóa dữ liệu thông qua đường dây điện xoay chiều 220V của nhà lưới — truyền tín hiệu qua đường điện lực</v>
       </c>
-      <c r="H25" t="str">
-        <v>Bắt buộc phải sử dụng các sợi dây cáp đồng có đường kính lõi lớn hơn 5mm — đường kính dây dẫn lõi lớn</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1149,19 +1149,19 @@
         <v>Tín hiệu vi sai truyền 2 dây ngược pha ($D+$ và $D-$). Nếu chiều dài 2 đường mạch trên PCB không bằng nhau (lệch pha Skew), sườn xung sẽ đến bộ thu lệch thời gian, triệt tiêu khả năng khử nhiễu đồng pha và gây méo dạng sóng. Không khớp trở kháng (thường thiết kế 90 Ohm cho USB, 100 Ohm cho Ethernet) sẽ gây phản xạ tín hiệu, làm tăng tỷ lệ lỗi bit (BER) ở tốc độ cao.</v>
       </c>
       <c r="E26" t="str">
+        <v>Để hệ điều hành của vi điều khiển tự động nâng tần số hoạt động của thạch anh lên gấp 10 lần — tăng tốc thạch anh</v>
+      </c>
+      <c r="F26" t="str">
         <v>Để tránh lệch pha thời gian (Skew) giữa hai tín hiệu vi sai gây méo mó dữ liệu và triệt tiêu tính chống nhiễu; trở kháng không khớp gây dội ngược tín hiệu phản xạ — cân bằng chiều dài và trở kháng đặc tính vi sai tốc độ cao</v>
       </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
         <v>Để đảm bảo dòng điện chạy qua hai dây dẫn luôn luôn bằng đúng 1 Ampe — dòng điện không đổi</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Để hệ điều hành của vi điều khiển tự động nâng tần số hoạt động của thạch anh lên gấp 10 lần — tăng tốc thạch anh</v>
       </c>
       <c r="H26" t="str">
         <v>Để ngăn chặn nước ẩm từ môi trường bên ngoài thấm vào bên trong mạch đồng — chống ẩm bảng mạch</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
